--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -8847,10 +8847,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118022407</v>
+        <v>118022366</v>
       </c>
       <c r="B70" t="n">
-        <v>102044</v>
+        <v>108703</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8859,52 +8859,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>701353</v>
+        <v>701112</v>
       </c>
       <c r="R70" t="n">
-        <v>6359389</v>
+        <v>6359275</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8937,11 +8923,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>30 cm hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8973,10 +8954,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118022366</v>
+        <v>118022407</v>
       </c>
       <c r="B71" t="n">
-        <v>108703</v>
+        <v>102044</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8985,38 +8966,52 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>701112</v>
+        <v>701353</v>
       </c>
       <c r="R71" t="n">
-        <v>6359275</v>
+        <v>6359389</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9049,6 +9044,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>30 cm hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -6828,10 +6828,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118022427</v>
+        <v>118022538</v>
       </c>
       <c r="B53" t="n">
-        <v>100097</v>
+        <v>57990</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6840,41 +6840,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>103055</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>701333</v>
+        <v>701298</v>
       </c>
       <c r="R53" t="n">
-        <v>6359501</v>
+        <v>6359287</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6914,11 +6923,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6935,10 +6939,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118022399</v>
+        <v>118022427</v>
       </c>
       <c r="B54" t="n">
-        <v>102044</v>
+        <v>100097</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6947,55 +6951,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6037533</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>701351</v>
+        <v>701333</v>
       </c>
       <c r="R54" t="n">
-        <v>6359353</v>
+        <v>6359501</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7027,11 +7017,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Mindre plantor.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7043,7 +7028,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7061,10 +7046,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118022395</v>
+        <v>118022475</v>
       </c>
       <c r="B55" t="n">
-        <v>102044</v>
+        <v>42953</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7073,25 +7058,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6037533</v>
+        <v>101242</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -7101,12 +7086,17 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7115,13 +7105,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>701356</v>
+        <v>701355</v>
       </c>
       <c r="R55" t="n">
-        <v>6359344</v>
+        <v>6359352</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7153,23 +7143,19 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>1 m hög.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7187,7 +7173,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118022401</v>
+        <v>118022348</v>
       </c>
       <c r="B56" t="n">
         <v>102044</v>
@@ -7241,10 +7227,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>701357</v>
+        <v>701238</v>
       </c>
       <c r="R56" t="n">
-        <v>6359355</v>
+        <v>6359519</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -7281,7 +7267,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>ca 3 m hög, stam 5 cm i diameter, fertil, död stam 4 cm med skott.</t>
+          <t>1,2 m hög.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7295,7 +7281,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7313,7 +7299,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118022404</v>
+        <v>118022408</v>
       </c>
       <c r="B57" t="n">
         <v>102044</v>
@@ -7348,7 +7334,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7367,13 +7353,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>701354</v>
+        <v>701358</v>
       </c>
       <c r="R57" t="n">
-        <v>6359377</v>
+        <v>6359389</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7407,7 +7393,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>4-5 m höga, spensliga, sterila =angripna.</t>
+          <t>40 cm hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7421,7 +7407,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7439,10 +7425,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118022371</v>
+        <v>118022399</v>
       </c>
       <c r="B58" t="n">
-        <v>106109</v>
+        <v>102044</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7451,41 +7437,55 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221849</v>
+        <v>6037533</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>701190</v>
+        <v>701351</v>
       </c>
       <c r="R58" t="n">
-        <v>6359305</v>
+        <v>6359353</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Tycks spridd l'ängs rävstig.</t>
+          <t>Mindre plantor.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar; gammalt grustag i strandvall ev.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7551,10 +7551,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118022473</v>
+        <v>118022405</v>
       </c>
       <c r="B59" t="n">
-        <v>42953</v>
+        <v>106765</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7567,41 +7567,36 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>101242</v>
+        <v>220079</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7610,13 +7605,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>701221</v>
+        <v>701354</v>
       </c>
       <c r="R59" t="n">
-        <v>6359309</v>
+        <v>6359384</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7654,13 +7649,12 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7678,10 +7672,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118022398</v>
+        <v>118022369</v>
       </c>
       <c r="B60" t="n">
-        <v>102044</v>
+        <v>108703</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7690,55 +7684,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>701355</v>
+        <v>701176</v>
       </c>
       <c r="R60" t="n">
-        <v>6359352</v>
+        <v>6359312</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7770,11 +7750,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>60 cm hög.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7786,7 +7761,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7804,7 +7779,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118022359</v>
+        <v>118022404</v>
       </c>
       <c r="B61" t="n">
         <v>102044</v>
@@ -7839,7 +7814,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7858,10 +7833,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700969</v>
+        <v>701354</v>
       </c>
       <c r="R61" t="n">
-        <v>6359361</v>
+        <v>6359377</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -7898,7 +7873,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>1,7 m hög.</t>
+          <t>4-5 m höga, spensliga, sterila =angripna.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7912,7 +7887,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7930,10 +7905,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118022408</v>
+        <v>118022371</v>
       </c>
       <c r="B62" t="n">
-        <v>102044</v>
+        <v>106109</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7942,52 +7917,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6037533</v>
+        <v>221849</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>701358</v>
+        <v>701190</v>
       </c>
       <c r="R62" t="n">
-        <v>6359389</v>
+        <v>6359305</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8024,7 +7985,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>40 cm hög. Flackare strandvall.</t>
+          <t>Tycks spridd l'ängs rävstig.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8038,7 +7999,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar; gammalt grustag i strandvall ev.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8056,10 +8017,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118022354</v>
+        <v>118022396</v>
       </c>
       <c r="B63" t="n">
-        <v>108703</v>
+        <v>102044</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8068,41 +8029,55 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>701029</v>
+        <v>701356</v>
       </c>
       <c r="R63" t="n">
-        <v>6359422</v>
+        <v>6359346</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8134,6 +8109,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>80 cm hög.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8145,7 +8125,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8163,10 +8143,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118022352</v>
+        <v>118022402</v>
       </c>
       <c r="B64" t="n">
-        <v>106109</v>
+        <v>102044</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8175,41 +8155,55 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221849</v>
+        <v>6037533</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>701072</v>
+        <v>701357</v>
       </c>
       <c r="R64" t="n">
-        <v>6359429</v>
+        <v>6359376</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8241,6 +8235,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>3,5 m (steril, angripen) + 4 m höga (fertil).</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8252,7 +8251,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8270,7 +8269,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118022362</v>
+        <v>118022401</v>
       </c>
       <c r="B65" t="n">
         <v>102044</v>
@@ -8324,10 +8323,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700964</v>
+        <v>701357</v>
       </c>
       <c r="R65" t="n">
-        <v>6359349</v>
+        <v>6359355</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -8364,7 +8363,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>1,2 m hög.</t>
+          <t>ca 3 m hög, stam 5 cm i diameter, fertil, död stam 4 cm med skott.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8378,7 +8377,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8396,10 +8395,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118022540</v>
+        <v>118022474</v>
       </c>
       <c r="B66" t="n">
-        <v>57303</v>
+        <v>42953</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8412,21 +8411,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>101242</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8434,9 +8433,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8445,13 +8454,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>701365</v>
+        <v>701336</v>
       </c>
       <c r="R66" t="n">
-        <v>6359342</v>
+        <v>6359312</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8489,8 +8498,14 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Barrskog med lundstarr.</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8507,10 +8522,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118022384</v>
+        <v>118022473</v>
       </c>
       <c r="B67" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8523,37 +8538,56 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>701278</v>
+        <v>701221</v>
       </c>
       <c r="R67" t="n">
-        <v>6359306</v>
+        <v>6359309</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8591,12 +8625,13 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8614,7 +8649,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118022394</v>
+        <v>118022366</v>
       </c>
       <c r="B68" t="n">
         <v>108703</v>
@@ -8654,10 +8689,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>701358</v>
+        <v>701112</v>
       </c>
       <c r="R68" t="n">
-        <v>6359325</v>
+        <v>6359275</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8721,7 +8756,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118022348</v>
+        <v>118022398</v>
       </c>
       <c r="B69" t="n">
         <v>102044</v>
@@ -8775,10 +8810,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>701238</v>
+        <v>701355</v>
       </c>
       <c r="R69" t="n">
-        <v>6359519</v>
+        <v>6359352</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>
@@ -8815,7 +8850,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>1,2 m hög.</t>
+          <t>60 cm hög.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8829,7 +8864,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8847,7 +8882,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118022366</v>
+        <v>118022384</v>
       </c>
       <c r="B70" t="n">
         <v>108703</v>
@@ -8887,10 +8922,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>701112</v>
+        <v>701278</v>
       </c>
       <c r="R70" t="n">
-        <v>6359275</v>
+        <v>6359306</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8954,10 +8989,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118022407</v>
+        <v>118022540</v>
       </c>
       <c r="B71" t="n">
-        <v>102044</v>
+        <v>57303</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8966,25 +9001,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6037533</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8992,14 +9027,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9008,13 +9038,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>701353</v>
+        <v>701365</v>
       </c>
       <c r="R71" t="n">
-        <v>6359389</v>
+        <v>6359342</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9046,11 +9076,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>30 cm hög. Flackare strandvall.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9059,11 +9084,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9080,7 +9100,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118022346</v>
+        <v>118022359</v>
       </c>
       <c r="B72" t="n">
         <v>102044</v>
@@ -9134,10 +9154,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>701238</v>
+        <v>700969</v>
       </c>
       <c r="R72" t="n">
-        <v>6359528</v>
+        <v>6359361</v>
       </c>
       <c r="S72" t="n">
         <v>3</v>
@@ -9174,7 +9194,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>1,1 m hög.</t>
+          <t>1,7 m hög.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9206,7 +9226,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118022376</v>
+        <v>118022362</v>
       </c>
       <c r="B73" t="n">
         <v>102044</v>
@@ -9260,13 +9280,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>701237</v>
+        <v>700964</v>
       </c>
       <c r="R73" t="n">
-        <v>6359313</v>
+        <v>6359349</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9300,7 +9320,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>1m hög; på åsrygg.</t>
+          <t>1,2 m hög.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9332,10 +9352,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118022388</v>
+        <v>118022352</v>
       </c>
       <c r="B74" t="n">
-        <v>108703</v>
+        <v>106109</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9348,16 +9368,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9372,10 +9392,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>701297</v>
+        <v>701072</v>
       </c>
       <c r="R74" t="n">
-        <v>6359321</v>
+        <v>6359429</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9439,10 +9459,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118022405</v>
+        <v>118022407</v>
       </c>
       <c r="B75" t="n">
-        <v>106765</v>
+        <v>102044</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9451,30 +9471,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220079</v>
+        <v>6037533</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9493,10 +9513,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>701354</v>
+        <v>701353</v>
       </c>
       <c r="R75" t="n">
-        <v>6359384</v>
+        <v>6359389</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9529,6 +9549,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>30 cm hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9560,10 +9585,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118022367</v>
+        <v>118022403</v>
       </c>
       <c r="B76" t="n">
-        <v>108703</v>
+        <v>102044</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9572,41 +9597,55 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>701152</v>
+        <v>701356</v>
       </c>
       <c r="R76" t="n">
-        <v>6359301</v>
+        <v>6359377</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9638,6 +9677,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>1,9 m + 2 m höga. Sterila=angripna.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9649,7 +9693,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9667,10 +9711,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118022406</v>
+        <v>118022388</v>
       </c>
       <c r="B77" t="n">
-        <v>102044</v>
+        <v>108703</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9679,52 +9723,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>701354</v>
+        <v>701297</v>
       </c>
       <c r="R77" t="n">
-        <v>6359384</v>
+        <v>6359321</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9757,11 +9787,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>3 småskott varav 1ex 1 m hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9793,10 +9818,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118022475</v>
+        <v>118022395</v>
       </c>
       <c r="B78" t="n">
-        <v>42953</v>
+        <v>102044</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9805,25 +9830,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>101242</v>
+        <v>6037533</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9833,17 +9858,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9852,13 +9872,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>701355</v>
+        <v>701356</v>
       </c>
       <c r="R78" t="n">
-        <v>6359352</v>
+        <v>6359344</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9890,19 +9910,23 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>1 m hög.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9920,7 +9944,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118022391</v>
+        <v>118022346</v>
       </c>
       <c r="B79" t="n">
         <v>102044</v>
@@ -9974,10 +9998,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>701336</v>
+        <v>701238</v>
       </c>
       <c r="R79" t="n">
-        <v>6359312</v>
+        <v>6359528</v>
       </c>
       <c r="S79" t="n">
         <v>3</v>
@@ -10014,7 +10038,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>1 m hög.</t>
+          <t>1,1 m hög.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10046,10 +10070,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118022474</v>
+        <v>118022394</v>
       </c>
       <c r="B80" t="n">
-        <v>42953</v>
+        <v>108703</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10062,56 +10086,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>701336</v>
+        <v>701358</v>
       </c>
       <c r="R80" t="n">
-        <v>6359312</v>
+        <v>6359325</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10149,13 +10154,12 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10173,10 +10177,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118022538</v>
+        <v>118022354</v>
       </c>
       <c r="B81" t="n">
-        <v>57990</v>
+        <v>108703</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10189,43 +10193,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103055</v>
+        <v>220299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>701298</v>
+        <v>701029</v>
       </c>
       <c r="R81" t="n">
-        <v>6359287</v>
+        <v>6359422</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10268,6 +10263,11 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Kalktallskog med mycket enbuskar.</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10284,7 +10284,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118022369</v>
+        <v>118022367</v>
       </c>
       <c r="B82" t="n">
         <v>108703</v>
@@ -10324,10 +10324,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>701176</v>
+        <v>701152</v>
       </c>
       <c r="R82" t="n">
-        <v>6359312</v>
+        <v>6359301</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10391,7 +10391,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118022396</v>
+        <v>118022391</v>
       </c>
       <c r="B83" t="n">
         <v>102044</v>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>701356</v>
+        <v>701336</v>
       </c>
       <c r="R83" t="n">
-        <v>6359346</v>
+        <v>6359312</v>
       </c>
       <c r="S83" t="n">
         <v>3</v>
@@ -10485,7 +10485,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>80 cm hög.</t>
+          <t>1 m hög.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10517,7 +10517,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118022403</v>
+        <v>118022406</v>
       </c>
       <c r="B84" t="n">
         <v>102044</v>
@@ -10552,7 +10552,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10571,13 +10571,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>701356</v>
+        <v>701354</v>
       </c>
       <c r="R84" t="n">
-        <v>6359377</v>
+        <v>6359384</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>1,9 m + 2 m höga. Sterila=angripna.</t>
+          <t>3 småskott varav 1ex 1 m hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10643,7 +10643,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118022402</v>
+        <v>118022376</v>
       </c>
       <c r="B85" t="n">
         <v>102044</v>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10697,13 +10697,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>701357</v>
+        <v>701237</v>
       </c>
       <c r="R85" t="n">
-        <v>6359376</v>
+        <v>6359313</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>3,5 m (steril, angripen) + 4 m höga (fertil).</t>
+          <t>1m hög; på åsrygg.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -6828,10 +6828,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118022538</v>
+        <v>118022348</v>
       </c>
       <c r="B53" t="n">
-        <v>57990</v>
+        <v>102046</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6840,25 +6840,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103055</v>
+        <v>6037533</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6866,9 +6866,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6877,13 +6882,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>701298</v>
+        <v>701238</v>
       </c>
       <c r="R53" t="n">
-        <v>6359287</v>
+        <v>6359519</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6915,6 +6920,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1,2 m hög.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6923,6 +6933,11 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Kalktallskog med mycket enbuskar.</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6939,10 +6954,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118022427</v>
+        <v>118022473</v>
       </c>
       <c r="B54" t="n">
-        <v>100097</v>
+        <v>42953</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6951,38 +6966,57 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>101242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>701333</v>
+        <v>701221</v>
       </c>
       <c r="R54" t="n">
-        <v>6359501</v>
+        <v>6359309</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7023,12 +7057,13 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7046,10 +7081,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118022475</v>
+        <v>118022367</v>
       </c>
       <c r="B55" t="n">
-        <v>42953</v>
+        <v>108705</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7062,53 +7097,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>701355</v>
+        <v>701152</v>
       </c>
       <c r="R55" t="n">
-        <v>6359352</v>
+        <v>6359301</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7149,13 +7165,12 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7173,10 +7188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118022348</v>
+        <v>118022384</v>
       </c>
       <c r="B56" t="n">
-        <v>102044</v>
+        <v>108705</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7185,55 +7200,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>701238</v>
+        <v>701278</v>
       </c>
       <c r="R56" t="n">
-        <v>6359519</v>
+        <v>6359306</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7263,11 +7264,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>1,2 m hög.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7299,10 +7295,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118022408</v>
+        <v>118022395</v>
       </c>
       <c r="B57" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7353,13 +7349,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>701358</v>
+        <v>701356</v>
       </c>
       <c r="R57" t="n">
-        <v>6359389</v>
+        <v>6359344</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7393,7 +7389,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>40 cm hög. Flackare strandvall.</t>
+          <t>1 m hög.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7407,7 +7403,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7425,10 +7421,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118022399</v>
+        <v>118022406</v>
       </c>
       <c r="B58" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7460,7 +7456,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7479,13 +7475,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>701351</v>
+        <v>701354</v>
       </c>
       <c r="R58" t="n">
-        <v>6359353</v>
+        <v>6359384</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7519,7 +7515,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Mindre plantor.</t>
+          <t>3 småskott varav 1ex 1 m hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7533,7 +7529,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7551,10 +7547,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118022405</v>
+        <v>118022398</v>
       </c>
       <c r="B59" t="n">
-        <v>106765</v>
+        <v>102046</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7563,30 +7559,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220079</v>
+        <v>6037533</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7605,13 +7601,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>701354</v>
+        <v>701355</v>
       </c>
       <c r="R59" t="n">
-        <v>6359384</v>
+        <v>6359352</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7643,6 +7639,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>60 cm hög.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7654,7 +7655,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7675,7 +7676,7 @@
         <v>118022369</v>
       </c>
       <c r="B60" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7779,10 +7780,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118022404</v>
+        <v>118022362</v>
       </c>
       <c r="B61" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7814,7 +7815,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7833,10 +7834,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>701354</v>
+        <v>700964</v>
       </c>
       <c r="R61" t="n">
-        <v>6359377</v>
+        <v>6359349</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -7873,7 +7874,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>4-5 m höga, spensliga, sterila =angripna.</t>
+          <t>1,2 m hög.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7887,7 +7888,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7905,10 +7906,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118022371</v>
+        <v>118022359</v>
       </c>
       <c r="B62" t="n">
-        <v>106109</v>
+        <v>102046</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7917,41 +7918,55 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221849</v>
+        <v>6037533</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>701190</v>
+        <v>700969</v>
       </c>
       <c r="R62" t="n">
-        <v>6359305</v>
+        <v>6359361</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7985,7 +8000,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Tycks spridd l'ängs rävstig.</t>
+          <t>1,7 m hög.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7999,7 +8014,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar; gammalt grustag i strandvall ev.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8017,10 +8032,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118022396</v>
+        <v>118022403</v>
       </c>
       <c r="B63" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8052,7 +8067,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8074,7 +8089,7 @@
         <v>701356</v>
       </c>
       <c r="R63" t="n">
-        <v>6359346</v>
+        <v>6359377</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -8111,7 +8126,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>80 cm hög.</t>
+          <t>1,9 m + 2 m höga. Sterila=angripna.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8125,7 +8140,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8143,10 +8158,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118022402</v>
+        <v>118022427</v>
       </c>
       <c r="B64" t="n">
-        <v>102044</v>
+        <v>100099</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8155,55 +8170,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6037533</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>701357</v>
+        <v>701333</v>
       </c>
       <c r="R64" t="n">
-        <v>6359376</v>
+        <v>6359501</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8235,11 +8236,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>3,5 m (steril, angripen) + 4 m höga (fertil).</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8251,7 +8247,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8269,10 +8265,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118022401</v>
+        <v>118022399</v>
       </c>
       <c r="B65" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8304,7 +8300,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8323,10 +8319,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>701357</v>
+        <v>701351</v>
       </c>
       <c r="R65" t="n">
-        <v>6359355</v>
+        <v>6359353</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -8363,7 +8359,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>ca 3 m hög, stam 5 cm i diameter, fertil, död stam 4 cm med skott.</t>
+          <t>Mindre plantor.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8395,10 +8391,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118022474</v>
+        <v>118022538</v>
       </c>
       <c r="B66" t="n">
-        <v>42953</v>
+        <v>57991</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8411,21 +8407,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>101242</v>
+        <v>103055</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8433,19 +8429,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8454,13 +8440,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>701336</v>
+        <v>701298</v>
       </c>
       <c r="R66" t="n">
-        <v>6359312</v>
+        <v>6359287</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8498,14 +8484,8 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Barrskog med lundstarr.</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8522,10 +8502,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118022473</v>
+        <v>118022354</v>
       </c>
       <c r="B67" t="n">
-        <v>42953</v>
+        <v>108705</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8538,56 +8518,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>701221</v>
+        <v>701029</v>
       </c>
       <c r="R67" t="n">
-        <v>6359309</v>
+        <v>6359422</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8625,13 +8586,12 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8649,10 +8609,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118022366</v>
+        <v>118022371</v>
       </c>
       <c r="B68" t="n">
-        <v>108703</v>
+        <v>106111</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8665,16 +8625,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8689,10 +8649,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>701112</v>
+        <v>701190</v>
       </c>
       <c r="R68" t="n">
-        <v>6359275</v>
+        <v>6359305</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8727,6 +8687,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Tycks spridd l'ängs rävstig.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8738,7 +8703,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar; gammalt grustag i strandvall ev.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8756,10 +8721,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118022398</v>
+        <v>118022407</v>
       </c>
       <c r="B69" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8810,13 +8775,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>701355</v>
+        <v>701353</v>
       </c>
       <c r="R69" t="n">
-        <v>6359352</v>
+        <v>6359389</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8850,7 +8815,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>60 cm hög.</t>
+          <t>30 cm hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8864,7 +8829,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8882,10 +8847,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118022384</v>
+        <v>118022394</v>
       </c>
       <c r="B70" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8922,10 +8887,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>701278</v>
+        <v>701358</v>
       </c>
       <c r="R70" t="n">
-        <v>6359306</v>
+        <v>6359325</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8989,10 +8954,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118022540</v>
+        <v>118022346</v>
       </c>
       <c r="B71" t="n">
-        <v>57303</v>
+        <v>102046</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9001,25 +8966,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6037533</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -9027,9 +8992,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9038,13 +9008,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>701365</v>
+        <v>701238</v>
       </c>
       <c r="R71" t="n">
-        <v>6359342</v>
+        <v>6359528</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9076,6 +9046,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>1,1 m hög.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9084,6 +9059,11 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Kalktallskog med mycket enbuskar.</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9100,10 +9080,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118022359</v>
+        <v>118022402</v>
       </c>
       <c r="B72" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9135,7 +9115,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9145,7 +9125,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9154,10 +9134,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>700969</v>
+        <v>701357</v>
       </c>
       <c r="R72" t="n">
-        <v>6359361</v>
+        <v>6359376</v>
       </c>
       <c r="S72" t="n">
         <v>3</v>
@@ -9194,7 +9174,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>1,7 m hög.</t>
+          <t>3,5 m (steril, angripen) + 4 m höga (fertil).</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9208,7 +9188,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. I förmodat fuktigare svacka mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9226,10 +9206,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118022362</v>
+        <v>118022401</v>
       </c>
       <c r="B73" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9280,10 +9260,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700964</v>
+        <v>701357</v>
       </c>
       <c r="R73" t="n">
-        <v>6359349</v>
+        <v>6359355</v>
       </c>
       <c r="S73" t="n">
         <v>3</v>
@@ -9320,7 +9300,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>1,2 m hög.</t>
+          <t>ca 3 m hög, stam 5 cm i diameter, fertil, död stam 4 cm med skott.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9334,7 +9314,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9352,10 +9332,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118022352</v>
+        <v>118022405</v>
       </c>
       <c r="B74" t="n">
-        <v>106109</v>
+        <v>106767</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9368,34 +9348,48 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>701072</v>
+        <v>701354</v>
       </c>
       <c r="R74" t="n">
-        <v>6359429</v>
+        <v>6359384</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9459,10 +9453,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118022407</v>
+        <v>118022475</v>
       </c>
       <c r="B75" t="n">
-        <v>102044</v>
+        <v>42953</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9471,25 +9465,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6037533</v>
+        <v>101242</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -9499,12 +9493,17 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9513,13 +9512,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>701353</v>
+        <v>701355</v>
       </c>
       <c r="R75" t="n">
-        <v>6359389</v>
+        <v>6359352</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9551,23 +9550,19 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>30 cm hög. Flackare strandvall.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9585,10 +9580,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118022403</v>
+        <v>118022404</v>
       </c>
       <c r="B76" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9620,7 +9615,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9639,7 +9634,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>701356</v>
+        <v>701354</v>
       </c>
       <c r="R76" t="n">
         <v>6359377</v>
@@ -9679,7 +9674,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>1,9 m + 2 m höga. Sterila=angripna.</t>
+          <t>4-5 m höga, spensliga, sterila =angripna.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9711,10 +9706,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118022388</v>
+        <v>118022366</v>
       </c>
       <c r="B77" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9751,10 +9746,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>701297</v>
+        <v>701112</v>
       </c>
       <c r="R77" t="n">
-        <v>6359321</v>
+        <v>6359275</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9818,10 +9813,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118022395</v>
+        <v>118022388</v>
       </c>
       <c r="B78" t="n">
-        <v>102044</v>
+        <v>108705</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9830,55 +9825,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>701356</v>
+        <v>701297</v>
       </c>
       <c r="R78" t="n">
-        <v>6359344</v>
+        <v>6359321</v>
       </c>
       <c r="S78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9910,11 +9891,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>1 m hög.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9926,7 +9902,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9944,10 +9920,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118022346</v>
+        <v>118022396</v>
       </c>
       <c r="B79" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9998,10 +9974,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>701238</v>
+        <v>701356</v>
       </c>
       <c r="R79" t="n">
-        <v>6359528</v>
+        <v>6359346</v>
       </c>
       <c r="S79" t="n">
         <v>3</v>
@@ -10038,7 +10014,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>1,1 m hög.</t>
+          <t>80 cm hög.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10052,7 +10028,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Kalktallskog med mycket enbuskar. Flack strandvall.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10070,10 +10046,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118022394</v>
+        <v>118022408</v>
       </c>
       <c r="B80" t="n">
-        <v>108703</v>
+        <v>102046</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10082,28 +10058,42 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
@@ -10113,7 +10103,7 @@
         <v>701358</v>
       </c>
       <c r="R80" t="n">
-        <v>6359325</v>
+        <v>6359389</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10146,6 +10136,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>40 cm hög. Flackare strandvall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10177,10 +10172,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118022354</v>
+        <v>118022352</v>
       </c>
       <c r="B81" t="n">
-        <v>108703</v>
+        <v>106111</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10193,16 +10188,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -10217,10 +10212,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>701029</v>
+        <v>701072</v>
       </c>
       <c r="R81" t="n">
-        <v>6359422</v>
+        <v>6359429</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10284,10 +10279,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118022367</v>
+        <v>118022391</v>
       </c>
       <c r="B82" t="n">
-        <v>108703</v>
+        <v>102046</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10296,41 +10291,55 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lojsta Båtels 1:12., Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>701152</v>
+        <v>701336</v>
       </c>
       <c r="R82" t="n">
-        <v>6359301</v>
+        <v>6359312</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10360,6 +10369,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>1 m hög.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10391,10 +10405,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118022391</v>
+        <v>118022376</v>
       </c>
       <c r="B83" t="n">
-        <v>102044</v>
+        <v>102046</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10445,13 +10459,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>701336</v>
+        <v>701237</v>
       </c>
       <c r="R83" t="n">
-        <v>6359312</v>
+        <v>6359313</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10485,7 +10499,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>1 m hög.</t>
+          <t>1m hög; på åsrygg.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10517,10 +10531,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118022406</v>
+        <v>118022540</v>
       </c>
       <c r="B84" t="n">
-        <v>102044</v>
+        <v>57304</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10529,40 +10543,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6037533</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10571,13 +10580,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>701354</v>
+        <v>701365</v>
       </c>
       <c r="R84" t="n">
-        <v>6359384</v>
+        <v>6359342</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10609,11 +10618,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>3 småskott varav 1ex 1 m hög. Flackare strandvall.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10622,11 +10626,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10643,10 +10642,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118022376</v>
+        <v>118022474</v>
       </c>
       <c r="B85" t="n">
-        <v>102044</v>
+        <v>42953</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10655,25 +10654,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6037533</v>
+        <v>101242</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10683,12 +10682,17 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10697,13 +10701,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>701237</v>
+        <v>701336</v>
       </c>
       <c r="R85" t="n">
-        <v>6359313</v>
+        <v>6359312</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10735,23 +10739,19 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>1m hög; på åsrygg.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -10279,10 +10279,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118022391</v>
+        <v>118022540</v>
       </c>
       <c r="B82" t="n">
-        <v>102046</v>
+        <v>57304</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10291,25 +10291,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6037533</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -10317,14 +10317,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10333,13 +10328,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>701336</v>
+        <v>701365</v>
       </c>
       <c r="R82" t="n">
-        <v>6359312</v>
+        <v>6359342</v>
       </c>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10371,11 +10366,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>1 m hög.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -10384,11 +10374,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10405,10 +10390,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118022376</v>
+        <v>118022474</v>
       </c>
       <c r="B83" t="n">
-        <v>102046</v>
+        <v>42953</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10417,25 +10402,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6037533</v>
+        <v>101242</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -10445,12 +10430,17 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10459,13 +10449,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>701237</v>
+        <v>701336</v>
       </c>
       <c r="R83" t="n">
-        <v>6359313</v>
+        <v>6359312</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10497,23 +10487,19 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>1m hög; på åsrygg.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalktallskog med mycket enbuskar.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10531,10 +10517,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118022540</v>
+        <v>118022391</v>
       </c>
       <c r="B84" t="n">
-        <v>57304</v>
+        <v>102046</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10543,25 +10529,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6037533</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10569,9 +10555,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10580,13 +10571,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>701365</v>
+        <v>701336</v>
       </c>
       <c r="R84" t="n">
-        <v>6359342</v>
+        <v>6359312</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10618,6 +10609,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>1 m hög.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10626,6 +10622,11 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Kalktallskog med mycket enbuskar.</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10642,10 +10643,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118022474</v>
+        <v>118022376</v>
       </c>
       <c r="B85" t="n">
-        <v>42953</v>
+        <v>102046</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10654,25 +10655,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>101242</v>
+        <v>6037533</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10682,17 +10683,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10701,13 +10697,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>701336</v>
+        <v>701237</v>
       </c>
       <c r="R85" t="n">
-        <v>6359312</v>
+        <v>6359313</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10739,19 +10735,23 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>1m hög; på åsrygg.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Kalktallskog med mycket enbuskar.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10767,6 +10767,381 @@
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>121391837</v>
+      </c>
+      <c r="B86" t="n">
+        <v>102286</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>701238</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6359523</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>I-Got-1586</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Bengt Carlsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>121391836</v>
+      </c>
+      <c r="B87" t="n">
+        <v>102286</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Lojsta Båtels 1:12, punkt 84 m 200 m SV, Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>700967</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6359356</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>I-Got-1587</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>2 träd vid koordinaterna 1652575 6359166 (1,2 m), 1652580 6359179 (1,7 m)</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Bengt Carlsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>121391839</v>
+      </c>
+      <c r="B88" t="n">
+        <v>102286</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Lojsta Båtels 1:12, punkt 84 m 265 m SO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>701368</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6359350</v>
+      </c>
+      <c r="S88" t="n">
+        <v>57</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>I-Got-1584</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>19 träd/plantor med koordinater 1652946 6359125 (1 m), 1652962 6359166 (mindre plantor), 1652964 6359202 (0,3 m), 1652965 6359190 (4–5 m), 1652965 6359197 (1 m + småskott), 1652966 6359165 (0,6 m), 1652967 6359157 (1 m), 1652967 6359159 (0,8 m), 1652967 6359190 (1,9 m + 2 m), 1652968 6359168 (3 m), 1652968 6359189 (3, 5 m + 4 m), 1652969 6359202 (0,4 m)</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Bengt Carlsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -10769,10 +10769,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121391837</v>
+        <v>121391836</v>
       </c>
       <c r="B86" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10814,14 +10814,14 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 200 m SV, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>701238</v>
+        <v>700967</v>
       </c>
       <c r="R86" t="n">
-        <v>6359523</v>
+        <v>6359356</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>I-Got-1586</t>
+          <t>I-Got-1587</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
+          <t>2 träd vid koordinaterna 1652575 6359166 (1,2 m), 1652580 6359179 (1,7 m)</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10894,10 +10894,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121391836</v>
+        <v>121391837</v>
       </c>
       <c r="B87" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10939,14 +10939,14 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 200 m SV, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>700967</v>
+        <v>701238</v>
       </c>
       <c r="R87" t="n">
-        <v>6359356</v>
+        <v>6359523</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>I-Got-1587</t>
+          <t>I-Got-1586</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>2 träd vid koordinaterna 1652575 6359166 (1,2 m), 1652580 6359179 (1,7 m)</t>
+          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11022,7 +11022,7 @@
         <v>121391839</v>
       </c>
       <c r="B88" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -10769,10 +10769,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121391836</v>
+        <v>121391837</v>
       </c>
       <c r="B86" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10814,14 +10814,14 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 200 m SV, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>700967</v>
+        <v>701238</v>
       </c>
       <c r="R86" t="n">
-        <v>6359356</v>
+        <v>6359523</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>I-Got-1587</t>
+          <t>I-Got-1586</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>2 träd vid koordinaterna 1652575 6359166 (1,2 m), 1652580 6359179 (1,7 m)</t>
+          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10894,10 +10894,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121391837</v>
+        <v>121391836</v>
       </c>
       <c r="B87" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10939,14 +10939,14 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 200 m SV, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>701238</v>
+        <v>700967</v>
       </c>
       <c r="R87" t="n">
-        <v>6359523</v>
+        <v>6359356</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>I-Got-1586</t>
+          <t>I-Got-1587</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
+          <t>2 träd vid koordinaterna 1652575 6359166 (1,2 m), 1652580 6359179 (1,7 m)</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11022,7 +11022,7 @@
         <v>121391839</v>
       </c>
       <c r="B88" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -10772,7 +10772,7 @@
         <v>121391837</v>
       </c>
       <c r="B86" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>121391836</v>
       </c>
       <c r="B87" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>121391839</v>
       </c>
       <c r="B88" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11068,10 +11068,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>701368</v>
+        <v>701354</v>
       </c>
       <c r="R88" t="n">
-        <v>6359350</v>
+        <v>6359351</v>
       </c>
       <c r="S88" t="n">
         <v>57</v>

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -10769,10 +10769,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121391837</v>
+        <v>121391839</v>
       </c>
       <c r="B86" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10814,17 +10814,17 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 265 m SO, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>701238</v>
+        <v>701354</v>
       </c>
       <c r="R86" t="n">
-        <v>6359523</v>
+        <v>6359351</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>I-Got-1586</t>
+          <t>I-Got-1584</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
+          <t>19 träd/plantor med koordinater 1652946 6359125 (1 m), 1652962 6359166 (mindre plantor), 1652964 6359202 (0,3 m), 1652965 6359190 (4–5 m), 1652965 6359197 (1 m + småskott), 1652966 6359165 (0,6 m), 1652967 6359157 (1 m), 1652967 6359159 (0,8 m), 1652967 6359190 (1,9 m + 2 m), 1652968 6359168 (3 m), 1652968 6359189 (3, 5 m + 4 m), 1652969 6359202 (0,4 m)</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10894,10 +10894,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121391836</v>
+        <v>121391837</v>
       </c>
       <c r="B87" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10939,14 +10939,14 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 200 m SV, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>700967</v>
+        <v>701238</v>
       </c>
       <c r="R87" t="n">
-        <v>6359356</v>
+        <v>6359523</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>I-Got-1587</t>
+          <t>I-Got-1586</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>2 träd vid koordinaterna 1652575 6359166 (1,2 m), 1652580 6359179 (1,7 m)</t>
+          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11019,10 +11019,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121391839</v>
+        <v>121391836</v>
       </c>
       <c r="B88" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11064,17 +11064,17 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 265 m SO, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 200 m SV, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>701354</v>
+        <v>700967</v>
       </c>
       <c r="R88" t="n">
-        <v>6359351</v>
+        <v>6359356</v>
       </c>
       <c r="S88" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>I-Got-1584</t>
+          <t>I-Got-1587</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>19 träd/plantor med koordinater 1652946 6359125 (1 m), 1652962 6359166 (mindre plantor), 1652964 6359202 (0,3 m), 1652965 6359190 (4–5 m), 1652965 6359197 (1 m + småskott), 1652966 6359165 (0,6 m), 1652967 6359157 (1 m), 1652967 6359159 (0,8 m), 1652967 6359190 (1,9 m + 2 m), 1652968 6359168 (3 m), 1652968 6359189 (3, 5 m + 4 m), 1652969 6359202 (0,4 m)</t>
+          <t>2 träd vid koordinaterna 1652575 6359166 (1,2 m), 1652580 6359179 (1,7 m)</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -10772,7 +10772,7 @@
         <v>121391839</v>
       </c>
       <c r="B86" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10894,10 +10894,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121391837</v>
+        <v>121391836</v>
       </c>
       <c r="B87" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10939,14 +10939,14 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 200 m SV, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>701238</v>
+        <v>700967</v>
       </c>
       <c r="R87" t="n">
-        <v>6359523</v>
+        <v>6359356</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>I-Got-1586</t>
+          <t>I-Got-1587</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
+          <t>2 träd vid koordinaterna 1652575 6359166 (1,2 m), 1652580 6359179 (1,7 m)</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11019,10 +11019,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121391836</v>
+        <v>121391837</v>
       </c>
       <c r="B88" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11064,14 +11064,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 200 m SV, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>700967</v>
+        <v>701238</v>
       </c>
       <c r="R88" t="n">
-        <v>6359356</v>
+        <v>6359523</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>I-Got-1587</t>
+          <t>I-Got-1586</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>2 träd vid koordinaterna 1652575 6359166 (1,2 m), 1652580 6359179 (1,7 m)</t>
+          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -10772,7 +10772,7 @@
         <v>121391839</v>
       </c>
       <c r="B86" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>121391836</v>
       </c>
       <c r="B87" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>121391837</v>
       </c>
       <c r="B88" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -10894,7 +10894,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121391836</v>
+        <v>121391837</v>
       </c>
       <c r="B87" t="n">
         <v>102320</v>
@@ -10939,14 +10939,14 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 200 m SV, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>700967</v>
+        <v>701238</v>
       </c>
       <c r="R87" t="n">
-        <v>6359356</v>
+        <v>6359523</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>I-Got-1587</t>
+          <t>I-Got-1586</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>2 träd vid koordinaterna 1652575 6359166 (1,2 m), 1652580 6359179 (1,7 m)</t>
+          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11019,7 +11019,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121391837</v>
+        <v>121391836</v>
       </c>
       <c r="B88" t="n">
         <v>102320</v>
@@ -11064,14 +11064,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 200 m SV, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>701238</v>
+        <v>700967</v>
       </c>
       <c r="R88" t="n">
-        <v>6359523</v>
+        <v>6359356</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>I-Got-1586</t>
+          <t>I-Got-1587</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
+          <t>2 träd vid koordinaterna 1652575 6359166 (1,2 m), 1652580 6359179 (1,7 m)</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -10894,7 +10894,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121391837</v>
+        <v>121391836</v>
       </c>
       <c r="B87" t="n">
         <v>102320</v>
@@ -10939,14 +10939,14 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 200 m SV, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>701238</v>
+        <v>700967</v>
       </c>
       <c r="R87" t="n">
-        <v>6359523</v>
+        <v>6359356</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>I-Got-1586</t>
+          <t>I-Got-1587</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
+          <t>2 träd vid koordinaterna 1652575 6359166 (1,2 m), 1652580 6359179 (1,7 m)</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11019,7 +11019,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121391836</v>
+        <v>121391837</v>
       </c>
       <c r="B88" t="n">
         <v>102320</v>
@@ -11064,14 +11064,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lojsta Båtels 1:12, punkt 84 m 200 m SV, Gtl</t>
+          <t>Lojsta Båtels 1:12, punkt 84 m 150 m O, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>700967</v>
+        <v>701238</v>
       </c>
       <c r="R88" t="n">
-        <v>6359356</v>
+        <v>6359523</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>I-Got-1587</t>
+          <t>I-Got-1586</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>2 träd vid koordinaterna 1652575 6359166 (1,2 m), 1652580 6359179 (1,7 m)</t>
+          <t>2 träd vid koordinaterna 1652851 6359333 (1,2 m), 1652851 6359342 (1,1 m)</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -8758,11 +8758,11 @@
         <v>118022540</v>
       </c>
       <c r="B69" t="n">
-        <v>57306</v>
+        <v>57497</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -8758,7 +8758,7 @@
         <v>118022540</v>
       </c>
       <c r="B69" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -10772,11 +10772,11 @@
         <v>121391836</v>
       </c>
       <c r="B86" t="n">
-        <v>102328</v>
+        <v>102612</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10897,11 +10897,11 @@
         <v>121391839</v>
       </c>
       <c r="B87" t="n">
-        <v>102328</v>
+        <v>102612</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11022,11 +11022,11 @@
         <v>121391837</v>
       </c>
       <c r="B88" t="n">
-        <v>102328</v>
+        <v>102612</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -8758,7 +8758,7 @@
         <v>118022540</v>
       </c>
       <c r="B69" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>121391836</v>
       </c>
       <c r="B86" t="n">
-        <v>102612</v>
+        <v>102630</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>121391839</v>
       </c>
       <c r="B87" t="n">
-        <v>102612</v>
+        <v>102630</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>121391837</v>
       </c>
       <c r="B88" t="n">
-        <v>102612</v>
+        <v>102630</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -8758,7 +8758,7 @@
         <v>118022540</v>
       </c>
       <c r="B69" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>121391836</v>
       </c>
       <c r="B86" t="n">
-        <v>102630</v>
+        <v>102632</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>121391839</v>
       </c>
       <c r="B87" t="n">
-        <v>102630</v>
+        <v>102632</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>121391837</v>
       </c>
       <c r="B88" t="n">
-        <v>102630</v>
+        <v>102632</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -10772,7 +10772,7 @@
         <v>121391836</v>
       </c>
       <c r="B86" t="n">
-        <v>102632</v>
+        <v>102207</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>121391839</v>
       </c>
       <c r="B87" t="n">
-        <v>102632</v>
+        <v>102207</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>121391837</v>
       </c>
       <c r="B88" t="n">
-        <v>102632</v>
+        <v>102207</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11142,6 +11142,714 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126382861</v>
+      </c>
+      <c r="B89" t="n">
+        <v>58371</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Lojsta Båtels 1:12, Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>701315</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6359368</v>
+      </c>
+      <c r="S89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Fanns här även 2024.</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126382775</v>
+      </c>
+      <c r="B90" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Lojsta  Båtels 1:12, Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>701315</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6359368</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Vid snitslad tall.</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126382899</v>
+      </c>
+      <c r="B91" t="n">
+        <v>58371</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Lojsta Båtels 1:12, Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>701064</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6359334</v>
+      </c>
+      <c r="S91" t="n">
+        <v>25</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>126382818</v>
+      </c>
+      <c r="B92" t="n">
+        <v>102485</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Lojsta  Båtels 1:12, Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>701315</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6359368</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>1,65 cm hög, stam 1 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126382722</v>
+      </c>
+      <c r="B93" t="n">
+        <v>102485</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Lojsta Båtels 1:12, Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>701310</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6359412</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>4 m hög, en grövre stam ca 4 cm i diameter plus tre smala stammar. Bladen är angripna av spinn.</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>126383015</v>
+      </c>
+      <c r="B94" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Lojsta Båtels 1:12, Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>700965</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6359387</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1836-2023 artfynd.xlsx
+++ b/artfynd/A 1836-2023 artfynd.xlsx
@@ -11147,7 +11147,7 @@
         <v>126382861</v>
       </c>
       <c r="B89" t="n">
-        <v>58371</v>
+        <v>58374</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>126382775</v>
       </c>
       <c r="B90" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>126382899</v>
       </c>
       <c r="B91" t="n">
-        <v>58371</v>
+        <v>58374</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>126382818</v>
       </c>
       <c r="B92" t="n">
-        <v>102485</v>
+        <v>102494</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>126382722</v>
       </c>
       <c r="B93" t="n">
-        <v>102485</v>
+        <v>102494</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>126383015</v>
       </c>
       <c r="B94" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
